--- a/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Full DTA loaded correctly at https://regplus.reganalytics.com/wta/FullDta with the expected heading and placeholder.</t>
+          <t>Full DTA loaded correctly at https://regplus.kaz.com.bd/wta/FullDta with the expected heading and placeholder.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the DTA table with the expected headers and 46 rows.</t>
+          <t>Selecting Australia rendered the DTA table with the expected headers and 53 rows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -747,94 +747,153 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>FullDta_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Treaties FullDta</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The country search box narrows the jurisdiction list by substring</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Full DTA.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Search text: Aus</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Full DTA
+2. Type 'Aus' into the search box
+3. Verify 'Australia' stays visible and 'Bangladesh' is filtered out</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'Aus' kept 'Australia' visible and filtered out non-matching 'Bangladesh', confirming the search box narrows the jurisdiction list.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Search narrows the list to matches only</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>FullDta_06</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Treaties FullDta</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>The 'Models' dropdown switches the table to a Model Tax Convention view</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Full DTA.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Model: OECD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
 2. Click 'Models', then 'OECD'
 3. Verify the Model Tax Convention view is shown</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Selecting 'OECD' from the Models dropdown switched the page to the OECD Model Tax Convention view.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] Model Tax Convention view is shown after selecting 'OECD'</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FullDta_07</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Treaties FullDta</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>A row's 'View' link opens the full treaty document viewer</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Full DTA.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
 2. Select Australia
@@ -842,59 +901,59 @@
 4. Verify the document viewer's 'Contents' sidebar and treaty title are shown</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>The Austria row's 'View' link correctly opened the full document viewer.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'View' link opens the full document viewer with the correct title and Contents sidebar</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FullDta_08</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Treaties FullDta</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>The document viewer's Export button downloads a real, non-empty PDF</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's document viewer open.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Full DTA, select Australia
 2. Open the Austria document viewer
@@ -902,22 +961,22 @@
 4. Verify a real, non-empty PDF download completed</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>The Export button downloaded 'Treaty_Australia - Austria.pdf' (90767 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>The Export button downloaded 'Treaty_Australia - Austria.pdf' (92230 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>[PASS] The document viewer's Export button downloads a real, non-empty .pdf file with no failure</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FullDta_01</t>
+          <t>FullDta_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full DTA page loads with the jurisdiction panel</t>
+          <t>The Australia DTA table lists a known treaty partner with its status</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load at /wta/FullDta with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
+          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Full DTA.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia, expected partner: Austria</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
-2. Verify URL, heading and placeholder text</t>
+2. Select Australia
+3. Verify a row for 'Austria' exists and shows 'In Force'</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load at /wta/FullDta with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
+          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Full DTA loaded correctly at https://regplus.kaz.com.bd/wta/FullDta with the expected heading and placeholder.</t>
+          <t>The DTA table includes an 'Austria' row showing 'In Force', as expected for a live treaty partner.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Full DTA loads with URL/heading/placeholder all present</t>
+          <t>[PASS] A row for 'Austria' exists and shows 'In Force'</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FullDta_02</t>
+          <t>FullDta_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +581,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders the DTA table with expected columns</t>
+          <t>Switching the 'Americas' region tab shows an Americas jurisdiction</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a table with columns ['', 'Partner Country', 'Status', 'Signature', 'Entry Into Force', 'Effective'] and at least one row.</t>
+          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -595,29 +596,29 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>Region: Americas, expected country: Canada</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
-2. Select Australia
-3. Verify the table headers and row count</t>
+2. Click the 'Americas' region tab
+3. Verify 'Canada' is visible in the jurisdiction list</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a table with columns ['', 'Partner Country', 'Status', 'Signature', 'Entry Into Force', 'Effective'] and at least one row.</t>
+          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the DTA table with the expected headers and 53 rows.</t>
+          <t>Switching to the 'Americas' region tab made 'Canada' visible in the jurisdiction list.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] DTA table shows the expected columns and at least one row</t>
+          <t>[PASS] 'Canada' is visible under the Americas region tab</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -629,7 +630,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FullDta_03</t>
+          <t>FullDta_05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -639,44 +640,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The Australia DTA table lists a known treaty partner with its status</t>
+          <t>The country search box narrows the jurisdiction list by substring</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
+          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Full DTA.</t>
+          <t>User is logged in and on Full DTA.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia, expected partner: Austria</t>
+          <t>Search text: Aus</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
-2. Select Australia
-3. Verify a row for 'Austria' exists and shows 'In Force'</t>
+2. Type 'Aus' into the search box
+3. Verify 'Australia' stays visible and 'Bangladesh' is filtered out</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
+          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The DTA table includes an 'Austria' row showing 'In Force', as expected for a live treaty partner.</t>
+          <t>Typing 'Aus' kept 'Australia' visible and filtered out non-matching 'Bangladesh', confirming the search box narrows the jurisdiction list.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] A row for 'Austria' exists and shows 'In Force'</t>
+          <t>[PASS] Search narrows the list to matches only</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -688,7 +689,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FullDta_04</t>
+          <t>FullDta_06</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -698,12 +699,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Switching the 'Americas' region tab shows an Americas jurisdiction</t>
+          <t>The 'Models' dropdown switches the table to a Model Tax Convention view</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
+          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -713,29 +714,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Region: Americas, expected country: Canada</t>
+          <t>Model: OECD</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
-2. Click the 'Americas' region tab
-3. Verify 'Canada' is visible in the jurisdiction list</t>
+2. Click 'Models', then 'OECD'
+3. Verify the Model Tax Convention view is shown</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
+          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Switching to the 'Americas' region tab made 'Canada' visible in the jurisdiction list.</t>
+          <t>Selecting 'OECD' from the Models dropdown switched the page to the OECD Model Tax Convention view.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Canada' is visible under the Americas region tab</t>
+          <t>[PASS] Model Tax Convention view is shown after selecting 'OECD'</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -747,7 +748,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FullDta_05</t>
+          <t>FullDta_07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -757,143 +758,25 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The country search box narrows the jurisdiction list by substring</t>
+          <t>A row's 'View' link opens the full treaty document viewer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
+          <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Full DTA.</t>
+          <t>User is logged in, Australia selected on Full DTA.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Search text: Aus</t>
+          <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Full DTA
-2. Type 'Aus' into the search box
-3. Verify 'Australia' stays visible and 'Bangladesh' is filtered out</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Aus' kept 'Australia' visible and filtered out non-matching 'Bangladesh', confirming the search box narrows the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Search narrows the list to matches only</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The 'Models' dropdown switches the table to a Model Tax Convention view</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Full DTA.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Model: OECD</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Full DTA
-2. Click 'Models', then 'OECD'
-3. Verify the Model Tax Convention view is shown</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Selecting 'OECD' from the Models dropdown switched the page to the OECD Model Tax Convention view.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Model Tax Convention view is shown after selecting 'OECD'</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>A row's 'View' link opens the full treaty document viewer</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Full DTA.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
 2. Select Australia
@@ -901,59 +784,59 @@
 4. Verify the document viewer's 'Contents' sidebar and treaty title are shown</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>The Austria row's 'View' link correctly opened the full document viewer.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'View' link opens the full document viewer with the correct title and Contents sidebar</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FullDta_08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Treaties FullDta</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>The document viewer's Export button downloads a real, non-empty PDF</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's document viewer open.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Full DTA, select Australia
 2. Open the Austria document viewer
@@ -961,22 +844,22 @@
 4. Verify a real, non-empty PDF download completed</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>The Export button downloaded 'Treaty_Australia - Austria.pdf' (92230 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>The Export button downloaded 'Treaty_Australia - Austria.pdf' (90773 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] The document viewer's Export button downloads a real, non-empty .pdf file with no failure</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties FullDta/Treaties FullDta_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FullDta_03</t>
+          <t>FullDta_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,44 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Australia DTA table lists a known treaty partner with its status</t>
+          <t>Full DTA page loads with the jurisdiction panel</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
+          <t>The page must load at /wta/FullDta with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Full DTA.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia, expected partner: Austria</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
-2. Select Australia
-3. Verify a row for 'Austria' exists and shows 'In Force'</t>
+2. Verify URL, heading and placeholder text</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>With Australia selected, the DTA table must include a row for 'Austria' whose status is 'In Force'.</t>
+          <t>The page must load at /wta/FullDta with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The DTA table includes an 'Austria' row showing 'In Force', as expected for a live treaty partner.</t>
+          <t>Full DTA loaded correctly at https://regplusrc.reganalytics.com/wta/FullDta with the expected heading and placeholder.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] A row for 'Austria' exists and shows 'In Force'</t>
+          <t>[PASS] Full DTA loads with URL/heading/placeholder all present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FullDta_04</t>
+          <t>FullDta_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,12 +580,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching the 'Americas' region tab shows an Americas jurisdiction</t>
+          <t>Selecting a jurisdiction renders the DTA table with expected columns</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
+          <t>Checking 'Australia' must render a table with columns ['', 'Partner Country', 'Status', 'Signature', 'Entry Into Force', 'Effective'] and at least one row.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,270 +595,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Region: Americas, expected country: Canada</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Full DTA
-2. Click the 'Americas' region tab
-3. Verify 'Canada' is visible in the jurisdiction list</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Americas' region tab must make a known Americas country (e.g. 'Canada') visible in the left jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Switching to the 'Americas' region tab made 'Canada' visible in the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Canada' is visible under the Americas region tab</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_05</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The country search box narrows the jurisdiction list by substring</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Full DTA.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Search text: Aus</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Full DTA
-2. Type 'Aus' into the search box
-3. Verify 'Australia' stays visible and 'Bangladesh' is filtered out</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Aus' into the search box must keep 'Australia' visible while filtering out 'Bangladesh' (which does not match).</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Typing 'Aus' kept 'Australia' visible and filtered out non-matching 'Bangladesh', confirming the search box narrows the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Search narrows the list to matches only</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_06</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The 'Models' dropdown switches the table to a Model Tax Convention view</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Full DTA.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Model: OECD</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Full DTA
-2. Click 'Models', then 'OECD'
-3. Verify the Model Tax Convention view is shown</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Models' then 'OECD' must replace the per-jurisdiction DTA table with the OECD Model Tax Convention list (the 'Model Tax Conventions: OECD' heading becomes visible).</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting 'OECD' from the Models dropdown switched the page to the OECD Model Tax Convention view.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Model Tax Convention view is shown after selecting 'OECD'</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_07</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>A row's 'View' link opens the full treaty document viewer</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Full DTA.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Full DTA
 2. Select Australia
-3. Click the Austria row's 'View' link
-4. Verify the document viewer's 'Contents' sidebar and treaty title are shown</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the Austria row's 'View' link (previously defined in the page object but never clicked by any test) must replace the table with the full document viewer - a 'Contents' sidebar and the treaty pair's title.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>The Austria row's 'View' link correctly opened the full document viewer.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The 'View' link opens the full document viewer with the correct title and Contents sidebar</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FullDta_08</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties FullDta</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The document viewer's Export button downloads a real, non-empty PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected, Austria's document viewer open.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Full DTA, select Australia
-2. Open the Austria document viewer
-3. Click the 'Export as PDF' button
-4. Verify a real, non-empty PDF download completed</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria document viewer open (Australia selected), clicking 'Export as PDF' must trigger a real download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>The Export button downloaded 'Treaty_Australia - Austria.pdf' (90773 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The document viewer's Export button downloads a real, non-empty .pdf file with no failure</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+3. Verify the table headers and row count</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' must render a table with columns ['', 'Partner Country', 'Status', 'Signature', 'Entry Into Force', 'Effective'] and at least one row.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Australia rendered the DTA table with the expected headers and 46 rows.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] DTA table shows the expected columns and at least one row</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
